--- a/xls/ANOVA.xlsx
+++ b/xls/ANOVA.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2024\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_C56A2A5E70C2052DCC3D4CE9BEF847810445FBF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F32807B5-D501-418A-9732-E03CEAE32DFC}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20115" windowHeight="8010"/>
+    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dado" sheetId="1" r:id="rId1"/>
@@ -18,12 +19,25 @@
     <sheet name="Bartlett" sheetId="3" r:id="rId4"/>
     <sheet name="Tukey" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>T1</t>
   </si>
@@ -126,22 +140,25 @@
     <t>q4,41 =</t>
   </si>
   <si>
-    <t>#http://www.dpi.inpe.br/~camilo/estatistica</t>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
+    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
+  </si>
+  <si>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,13 +188,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -360,14 +370,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -418,31 +427,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +463,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -801,6 +803,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-728E-4DDE-9438-97AB20E5CDB9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -847,6 +854,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-728E-4DDE-9438-97AB20E5CDB9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -913,7 +925,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -1253,6 +1265,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7729-475F-9851-B9E18876007F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1335,6 +1352,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7729-475F-9851-B9E18876007F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1401,7 +1423,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -1475,6 +1497,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3AB9-4AF5-BC66-9D8C4AD8BB99}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1557,6 +1584,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3AB9-4AF5-BC66-9D8C4AD8BB99}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1623,7 +1655,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -1963,6 +1995,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0A01-491D-9C66-672A9A8B684E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2029,7 +2066,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -2094,6 +2131,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0E0A-48AC-ACF1-00DA49F54A95}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2198,7 +2240,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="39" name="Gráfico 38"/>
+        <xdr:cNvPr id="39" name="Gráfico 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2228,7 +2276,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="40" name="Gráfico 39"/>
+        <xdr:cNvPr id="40" name="Gráfico 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -2260,7 +2314,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="41" name="Gráfico 40"/>
+        <xdr:cNvPr id="41" name="Gráfico 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -2292,7 +2352,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="42" name="Gráfico 41"/>
+        <xdr:cNvPr id="42" name="Gráfico 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -2501,7 +2567,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2673,9 +2745,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2713,9 +2785,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2750,7 +2822,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2785,7 +2857,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2958,284 +3030,287 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1"/>
-      <c r="H1" s="33" t="s">
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>12.7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>9.4</v>
+      </c>
+      <c r="E2" s="7">
+        <v>15.7</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="H2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="7">
-        <v>6.8</v>
-      </c>
-      <c r="C2" s="12">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="6">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C3" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="D3" s="11">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7">
+        <v>13.9</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="C4" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="D4" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="E4" s="7">
+        <v>13.7</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="6">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="C5" s="11">
+        <v>14.9</v>
+      </c>
+      <c r="D5" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E5" s="7">
+        <v>20.9</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
+        <v>10.7</v>
+      </c>
+      <c r="C6" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="D6" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="E6" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
+        <v>13.7</v>
+      </c>
+      <c r="C7" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E7" s="7">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="6">
+        <v>9</v>
+      </c>
+      <c r="C8" s="11">
+        <v>18.7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E8" s="7">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
+        <v>12.1</v>
+      </c>
+      <c r="C9" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="D9" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="E9" s="7">
+        <v>11.4</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
+        <v>13.4</v>
+      </c>
+      <c r="C10" s="11">
+        <v>19.3</v>
+      </c>
+      <c r="D10" s="11">
+        <v>13</v>
+      </c>
+      <c r="E10" s="7">
+        <v>21.6</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="C11" s="11">
+        <v>13.9</v>
+      </c>
+      <c r="D11" s="11">
+        <v>9.1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>10</v>
+      </c>
+      <c r="C12" s="11">
+        <v>13.7</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="7">
         <v>12.7</v>
       </c>
-      <c r="D2" s="12">
-        <v>9.4</v>
-      </c>
-      <c r="E2" s="8">
-        <v>15.7</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="H2" s="33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="7">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C3" s="12">
-        <v>13.5</v>
-      </c>
-      <c r="D3" s="12">
-        <v>13</v>
-      </c>
-      <c r="E3" s="8">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
         <v>13.9</v>
       </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="C4" s="12">
-        <v>12.9</v>
-      </c>
-      <c r="D4" s="12">
-        <v>12.1</v>
-      </c>
-      <c r="E4" s="8">
-        <v>13.7</v>
-      </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="C5" s="12">
-        <v>14.9</v>
-      </c>
-      <c r="D5" s="12">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E5" s="8">
-        <v>20.9</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="7">
-        <v>10.7</v>
-      </c>
-      <c r="C6" s="12">
-        <v>12.8</v>
-      </c>
-      <c r="D6" s="12">
-        <v>7.2</v>
-      </c>
-      <c r="E6" s="8">
-        <v>15.8</v>
-      </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="7">
-        <v>13.7</v>
-      </c>
-      <c r="C7" s="12">
-        <v>11.6</v>
-      </c>
-      <c r="D7" s="12">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E7" s="8">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="7">
-        <v>9</v>
-      </c>
-      <c r="C8" s="12">
-        <v>18.7</v>
-      </c>
-      <c r="D8" s="12">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="E8" s="8">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="7">
-        <v>12.1</v>
-      </c>
-      <c r="C9" s="12">
-        <v>10.1</v>
-      </c>
-      <c r="D9" s="12">
-        <v>14.8</v>
-      </c>
-      <c r="E9" s="8">
-        <v>11.4</v>
-      </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="7">
-        <v>13.4</v>
-      </c>
-      <c r="C10" s="12">
-        <v>19.3</v>
-      </c>
-      <c r="D10" s="12">
-        <v>13</v>
-      </c>
-      <c r="E10" s="8">
-        <v>21.6</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="C11" s="12">
-        <v>13.9</v>
-      </c>
-      <c r="D11" s="12">
-        <v>9.1</v>
-      </c>
-      <c r="E11" s="8">
-        <v>14.4</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="7">
-        <v>10</v>
-      </c>
-      <c r="C12" s="12">
-        <v>13.7</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="8">
-        <v>12.7</v>
-      </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="7">
-        <v>13.9</v>
-      </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>16.8</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="16" t="s">
+      <c r="D13" s="11"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <f>COUNT(B2:B13)</f>
         <v>12</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f t="shared" ref="C14:E14" si="0">COUNT(C2:C13)</f>
         <v>12</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <f>SUM(B14:E14)</f>
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="17">
         <f>SUM(B2:B13)</f>
         <v>128</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <f t="shared" ref="C15:E15" si="1">SUM(C2:C13)</f>
         <v>170.89999999999998</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="18">
         <f t="shared" si="1"/>
         <v>106.89999999999999</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <f t="shared" si="1"/>
         <v>174.6</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <f>SUM(B15:E15)</f>
         <v>580.4</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <f>B15/B14</f>
         <v>10.666666666666666</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="12">
         <f t="shared" ref="C16:E16" si="2">C15/C14</f>
         <v>14.241666666666665</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <f t="shared" si="2"/>
         <v>10.69</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f t="shared" si="2"/>
         <v>15.872727272727273</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <f>F15/F14</f>
         <v>12.897777777777778</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="28"/>
+      <c r="D19" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3244,7 +3319,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:E46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3369,7 +3444,7 @@
         <f>dado!B13</f>
         <v>13.9</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3422,7 +3497,7 @@
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="26">
         <f>dado!F16</f>
         <v>12.897777777777778</v>
       </c>
@@ -3439,7 +3514,7 @@
       <c r="D19">
         <v>8</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="26">
         <f>E18</f>
         <v>12.897777777777778</v>
       </c>
@@ -3466,7 +3541,7 @@
       <c r="D21">
         <v>0.5</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="26">
         <f>dado!B16</f>
         <v>10.666666666666666</v>
       </c>
@@ -3483,7 +3558,7 @@
       <c r="D22">
         <v>1.5</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="26">
         <f>E21</f>
         <v>10.666666666666666</v>
       </c>
@@ -3511,7 +3586,7 @@
         <f>D21+2</f>
         <v>2.5</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="26">
         <f>dado!C16</f>
         <v>14.241666666666665</v>
       </c>
@@ -3529,7 +3604,7 @@
         <f>D22+2</f>
         <v>3.5</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="26">
         <f>E24</f>
         <v>14.241666666666665</v>
       </c>
@@ -3556,7 +3631,7 @@
         <f>D24+2</f>
         <v>4.5</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="26">
         <f>dado!D16</f>
         <v>10.69</v>
       </c>
@@ -3574,7 +3649,7 @@
         <f>D25+2</f>
         <v>5.5</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="26">
         <f>E27</f>
         <v>10.69</v>
       </c>
@@ -3602,7 +3677,7 @@
         <f>D27+2</f>
         <v>6.5</v>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="26">
         <f>dado!E16</f>
         <v>15.872727272727273</v>
       </c>
@@ -3620,7 +3695,7 @@
         <f>D28+2</f>
         <v>7.5</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="26">
         <f>E30</f>
         <v>15.872727272727273</v>
       </c>
@@ -3781,7 +3856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3795,92 +3870,91 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <f>dado!B15^2/dado!B14+dado!C15^2/dado!C14+dado!D15^2/dado!D14+dado!E15^2/dado!E14-dado!F15^2/dado!F14</f>
         <v>227.5031262626253</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="1">
         <f>COUNTA(dado!B1:E1)-1</f>
         <v>3</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="22">
         <f>B3/C3</f>
         <v>75.834375420875105</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="22">
         <f>D3/D4</f>
         <v>10.557348624419454</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="23">
         <f>1-_xlfn.F.DIST(E3,C3,C4,1)</f>
         <v>2.8339003778965477E-5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="22">
         <f>B6-B3</f>
         <v>294.50665151515295</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="1">
         <f>C6-C3</f>
         <v>41</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <f>B4/C4</f>
         <v>7.1830890613451936</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="24"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="24">
         <f>SUMSQ(dado!B2:E13)-dado!F15^2/dado!F14</f>
         <v>522.00977777777825</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="25">
         <f>dado!F14-1</f>
         <v>44</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3888,7 +3962,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3898,111 +3972,111 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="1">
         <f>dado!B14</f>
         <v>12</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="1">
         <f>dado!B15</f>
         <v>128</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="22">
         <f>dado!B16</f>
         <v>10.666666666666666</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="1">
         <f>_xlfn.VAR.S(dado!B2:B13)</f>
         <v>5.0042424242424204</v>
       </c>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="1">
         <f>dado!C14</f>
         <v>12</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="1">
         <f>dado!C15</f>
         <v>170.89999999999998</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <f>dado!C16</f>
         <v>14.241666666666665</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="1">
         <f>_xlfn.VAR.S(dado!C2:C13)</f>
         <v>7.6171969696969919</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="1">
         <f>dado!D14</f>
         <v>10</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="1">
         <f>dado!D15</f>
         <v>106.89999999999999</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="22">
         <f>dado!D16</f>
         <v>10.69</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="1">
         <f>_xlfn.VAR.S(dado!D2:D13)</f>
         <v>5.8521111111110962</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="25">
         <f>dado!E14</f>
         <v>11</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="25">
         <f>dado!E15</f>
         <v>174.6</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="24">
         <f>dado!E16</f>
         <v>15.872727272727273</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="25">
         <f>_xlfn.VAR.S(dado!E2:E13)</f>
         <v>10.300181818181864</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B8">
@@ -4011,7 +4085,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B9">
@@ -4020,37 +4094,37 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="26">
         <f>ANOVA!D4</f>
         <v>7.1830890613451936</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="27">
         <f t="array" ref="B11">1+(SUM(1/(B3:B6-1))-1/(B9-B8))/(3*(B8-1))</f>
         <v>1.040948783225206</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="27">
         <f t="array" ref="B12">2.302585*((B9-B8)*LOG10(B10)-SUM((B3:B6-1)*LOG10(E3:E6)))/B11</f>
         <v>1.5086556543666196</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="27">
         <f>1-_xlfn.CHISQ.DIST(B12,B8-1,1)</f>
         <v>0.68027405556654175</v>
       </c>
@@ -4061,7 +4135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4080,61 +4154,61 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="26">
         <f>dado!B16</f>
         <v>10.666666666666666</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="26">
         <f>dado!D16</f>
         <v>10.69</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="26">
         <f>B3-B2</f>
         <v>2.3333333333333428E-2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="26">
         <f>dado!C16</f>
         <v>14.241666666666665</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="26">
         <f>B4-B2</f>
         <v>3.5749999999999993</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="26">
         <f>B4-B3</f>
         <v>3.5516666666666659</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="26">
         <f>dado!E16</f>
         <v>15.872727272727273</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="26">
         <f>B5-B2</f>
         <v>5.2060606060606069</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="26">
         <f>B5-B3</f>
         <v>5.1827272727272735</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="26">
         <f>B5-B4</f>
         <v>1.6310606060606077</v>
       </c>
@@ -4162,7 +4236,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="str">
+      <c r="A9" s="1" t="str">
         <f>A2</f>
         <v>T1</v>
       </c>
@@ -4172,7 +4246,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="str">
+      <c r="A10" s="1" t="str">
         <f t="shared" ref="A10" si="1">A3</f>
         <v>T3</v>
       </c>
@@ -4180,15 +4254,15 @@
         <f>Bartlett!B5</f>
         <v>10</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="28">
         <f>$C$15*SQRT($C$14*(1/B$9+1/B10))/SQRT(2)</f>
         <v>3.0786383266174782</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="str">
+      <c r="A11" s="1" t="str">
         <f t="shared" ref="A11" si="2">A4</f>
         <v>T2</v>
       </c>
@@ -4196,18 +4270,18 @@
         <f>Bartlett!B4</f>
         <v>12</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="28">
         <f t="shared" ref="C11:C12" si="3">$C$15*SQRT($C$14*(1/B$9+1/B11))/SQRT(2)</f>
         <v>2.9353664702474185</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="28">
         <f>$C$15*SQRT($C$14*(1/B$10+1/B11))/SQRT(2)</f>
         <v>3.0786383266174782</v>
       </c>
-      <c r="E11" s="30"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="str">
+      <c r="A12" s="1" t="str">
         <f t="shared" ref="A12" si="4">A5</f>
         <v>T4</v>
       </c>
@@ -4215,28 +4289,28 @@
         <f>Bartlett!B6</f>
         <v>11</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="28">
         <f t="shared" si="3"/>
         <v>3.0013379988766085</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="28">
         <f>$C$15*SQRT($C$14*(1/B$10+1/B12))/SQRT(2)</f>
         <v>3.141602682543724</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="28">
         <f>$C$15*SQRT($C$14*(1/B$11+1/B12))/SQRT(2)</f>
         <v>3.0013379988766085</v>
       </c>
-      <c r="L12" s="32"/>
+      <c r="L12" s="29"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L13" s="32"/>
+      <c r="L13" s="29"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="26">
         <f>ANOVA!D4</f>
         <v>7.1830890613451936</v>
       </c>

--- a/xls/ANOVA.xlsx
+++ b/xls/ANOVA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_C56A2A5E70C2052DCC3D4CE9BEF847810445FBF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F32807B5-D501-418A-9732-E03CEAE32DFC}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_C56A2A5E70C2052DCC3D4CE9BEF847810445FBF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D33EDDE-2930-4BB2-8895-415645A4D053}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dado" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>T1</t>
   </si>
@@ -140,13 +140,10 @@
     <t>q4,41 =</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
   <si>
-    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
-  </si>
-  <si>
-    <t>#https://cdrenno.github.io/Estatistica/</t>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
@@ -3049,7 +3046,7 @@
       </c>
       <c r="F1" s="1"/>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3067,7 +3064,7 @@
       </c>
       <c r="F2" s="1"/>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3084,9 +3081,6 @@
         <v>13.9</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="6">
